--- a/docs/Papers/iot_sensor_papers.xlsx
+++ b/docs/Papers/iot_sensor_papers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\PycharmProjects\bachelorThesis\Results\Papers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\PycharmProjects\bachelorThesis\docs\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90AFCA7-D28A-4F8B-8F78-4603924D1831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8C8A33-78EB-4A9D-963D-5E801F562BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="-5385" windowWidth="18240" windowHeight="29040" xr2:uid="{4BB29169-61E1-4DE9-82FD-04B604469E05}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{4BB29169-61E1-4DE9-82FD-04B604469E05}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Reference</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Rusu, C. A., Melhem, R., &amp; Mosse, D. (2003). Maximizing the system value while satisfying time and energy constraints. IBM Journal of Research and Development, 47(5.6), 689-702.</t>
+  </si>
+  <si>
+    <t>MICAz Datasheet</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E626032-7D24-48C2-9499-FD2EFC8C1634}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="68.85546875" customWidth="1"/>
@@ -773,6 +776,17 @@
       </c>
       <c r="D24" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -800,8 +814,9 @@
     <hyperlink ref="A22" r:id="rId21" xr:uid="{5F3BCD90-0B65-4DAA-A665-58BA38162C76}"/>
     <hyperlink ref="A23" r:id="rId22" xr:uid="{8C5183D0-E4C9-458B-8558-4109679B5E0B}"/>
     <hyperlink ref="A24" r:id="rId23" xr:uid="{503B01CC-4035-42EB-B635-F6BC7DB64AB7}"/>
+    <hyperlink ref="A25" r:id="rId24" display="MicaZ Datasheet" xr:uid="{53FC7695-21E4-4BCA-A726-ADDD3AA4E449}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId24"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId25"/>
 </worksheet>
 </file>
--- a/docs/Papers/iot_sensor_papers.xlsx
+++ b/docs/Papers/iot_sensor_papers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\PycharmProjects\bachelorThesis\docs\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8C8A33-78EB-4A9D-963D-5E801F562BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A69349-AAB1-4D47-BFBB-4F897E994981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{4BB29169-61E1-4DE9-82FD-04B604469E05}"/>
+    <workbookView xWindow="-18120" yWindow="-120" windowWidth="18240" windowHeight="29040" xr2:uid="{4BB29169-61E1-4DE9-82FD-04B604469E05}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
   <si>
     <t>Reference</t>
   </si>
@@ -129,6 +129,18 @@
   </si>
   <si>
     <t>MICAz Datasheet</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Caruso, A., Chessa, S., Escolar, S., Rincón, F., &amp; López, J. C. (2022, June). Task scheduling stabilization for solar energy harvesting internet of things devices. In 2022 IEEE Symposium on Computers and Communications (ISCC) (pp. 1-6). IEEE.</t>
+  </si>
+  <si>
+    <t>Refs. Caruso, A., Chessa, S., Escolar, S., Del Toro, X., &amp; López, J. C. (2018). A dynamic programming algorithm for high-level task scheduling in energy harvesting IoT. IEEE Internet of Things Journal, 5(3), 2234-2248.</t>
+  </si>
+  <si>
+    <t>Caruso, A., Chessa, S., Escolar, S., Del Toro, X., &amp; López, J. C. (2018). A dynamic programming algorithm for high-level task scheduling in energy harvesting IoT. IEEE Internet of Things Journal, 5(3), 2234-2248.</t>
   </si>
 </sst>
 </file>
@@ -521,13 +533,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E626032-7D24-48C2-9499-FD2EFC8C1634}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="68.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -540,7 +552,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -551,7 +563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -561,8 +573,11 @@
       <c r="G3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -572,8 +587,11 @@
       <c r="G4">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -583,8 +601,11 @@
       <c r="G5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -594,8 +615,11 @@
       <c r="G6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -606,7 +630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -616,8 +640,11 @@
       <c r="G8">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -628,7 +655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -639,7 +666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -649,8 +676,11 @@
       <c r="G11">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -661,7 +691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -672,7 +702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -682,8 +712,11 @@
       <c r="G14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -691,7 +724,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -702,7 +735,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -713,7 +746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -723,8 +756,11 @@
       <c r="G18">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -735,7 +771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
@@ -746,7 +782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
@@ -754,7 +790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -762,7 +798,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>28</v>
       </c>
@@ -770,7 +806,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>29</v>
       </c>
@@ -778,7 +814,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>30</v>
       </c>
@@ -787,6 +823,31 @@
       </c>
       <c r="G25">
         <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26">
+        <v>3</v>
+      </c>
+      <c r="H26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27">
+        <v>3</v>
+      </c>
+      <c r="H27" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -815,8 +876,10 @@
     <hyperlink ref="A23" r:id="rId22" xr:uid="{8C5183D0-E4C9-458B-8558-4109679B5E0B}"/>
     <hyperlink ref="A24" r:id="rId23" xr:uid="{503B01CC-4035-42EB-B635-F6BC7DB64AB7}"/>
     <hyperlink ref="A25" r:id="rId24" display="MicaZ Datasheet" xr:uid="{53FC7695-21E4-4BCA-A726-ADDD3AA4E449}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{87A34291-B855-4E91-88B0-CDD108182686}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{56F4A2A0-EDFB-46BC-B3F6-18F442D8617E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId25"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId27"/>
 </worksheet>
 </file>
--- a/docs/Papers/iot_sensor_papers.xlsx
+++ b/docs/Papers/iot_sensor_papers.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Roman\PycharmProjects\bachelorThesis\docs\Papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4A69349-AAB1-4D47-BFBB-4F897E994981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7200784E-A130-40C5-9029-B1F5FB432FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18120" yWindow="-120" windowWidth="18240" windowHeight="29040" xr2:uid="{4BB29169-61E1-4DE9-82FD-04B604469E05}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
   <si>
     <t>Reference</t>
   </si>
@@ -141,6 +141,21 @@
   </si>
   <si>
     <t>Caruso, A., Chessa, S., Escolar, S., Del Toro, X., &amp; López, J. C. (2018). A dynamic programming algorithm for high-level task scheduling in energy harvesting IoT. IEEE Internet of Things Journal, 5(3), 2234-2248.</t>
+  </si>
+  <si>
+    <t>Sixdenier, P. L., Wildermann, S., &amp; Teich, J. (2024, June). GRES: Guaranteed Remaining Energy Scheduling of Energy-harvesting Sensors by Quality Adaptation. In 2024 13th Mediterranean Conference on Embedded Computing (MECO) (pp. 1-5). IEEE.</t>
+  </si>
+  <si>
+    <t>Ait Aoudia, F., Gautier, M., &amp; Berder, O. (2018). RLMan: An energy manager based on reinforcement learning for energy harvesting wireless sensor networks. IEEE Transactions on Green Communications and Networking, 2(2), 408-417.</t>
+  </si>
+  <si>
+    <t>Basaklar, T., Tuncel, Y., &amp; Ogras, U. Y. (2022). tinyMAN: Lightweight energy manager using reinforcement learning for energy harvesting wearable IoT devices. arXiv preprint arXiv:2202.09297.</t>
+  </si>
+  <si>
+    <t>Tan, Y., Liu, W., &amp; Qiu, Q. (2009, November). Adaptive power management using reinforcement learning. In Proceedings of the 2009 international conference on computer-aided design (pp. 461-467).</t>
+  </si>
+  <si>
+    <t>Kulau, U., van Balen, J., Schildt, S., Büsching, F., &amp; Wolf, L. (2016, December). Dynamic sample rate adaptation for long-term IoT sensing applications. In 2016 IEEE 3rd World Forum on Internet of Things (WF-IoT) (pp. 271-276). IEEE.</t>
   </si>
 </sst>
 </file>
@@ -533,7 +548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E626032-7D24-48C2-9499-FD2EFC8C1634}">
   <sheetPr codeName="Tabelle1"/>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="68.85546875" customWidth="1"/>
@@ -629,6 +644,9 @@
       <c r="G7">
         <v>2</v>
       </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
@@ -701,6 +719,9 @@
       <c r="G13">
         <v>2</v>
       </c>
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
@@ -734,6 +755,9 @@
       <c r="G16">
         <v>2</v>
       </c>
+      <c r="H16" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
@@ -848,6 +872,37 @@
       </c>
       <c r="H27" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28">
+        <v>3</v>
+      </c>
+      <c r="H28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -878,8 +933,13 @@
     <hyperlink ref="A25" r:id="rId24" display="MicaZ Datasheet" xr:uid="{53FC7695-21E4-4BCA-A726-ADDD3AA4E449}"/>
     <hyperlink ref="A26" r:id="rId25" xr:uid="{87A34291-B855-4E91-88B0-CDD108182686}"/>
     <hyperlink ref="A27" r:id="rId26" xr:uid="{56F4A2A0-EDFB-46BC-B3F6-18F442D8617E}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{E22E3B62-DBC3-4169-B4A8-25781A5BE073}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{70CA1ECA-8202-4DD8-96CC-BDAE441B2958}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{F4409E38-E9F9-47D6-8865-0177C7DD27A3}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{0E406638-0242-4DA1-9C4C-679276756BDF}"/>
+    <hyperlink ref="A32" r:id="rId31" xr:uid="{9AAE3623-44C1-403D-A01E-17C19EDE7EF1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId27"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId32"/>
 </worksheet>
 </file>